--- a/src/test/resources/testdata/data.xlsx
+++ b/src/test/resources/testdata/data.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CloneGitHub\AutoAPI_RestAssuredTestNG\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9381FFEA-808A-4D77-9E13-EB3E00A6CECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{221BB185-2329-43B1-BAA1-1DE100A601C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RegisterUser" sheetId="1" r:id="rId1"/>
+    <sheet name="Category" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="36">
   <si>
     <t>USERNAME</t>
   </si>
@@ -60,30 +61,6 @@
     <t>09123456789</t>
   </si>
   <si>
-    <t>philong141008</t>
-  </si>
-  <si>
-    <t>philong141008@gmail.com</t>
-  </si>
-  <si>
-    <t>philong141009</t>
-  </si>
-  <si>
-    <t>philong141010</t>
-  </si>
-  <si>
-    <t>philong141011</t>
-  </si>
-  <si>
-    <t>philong141009@gmail.com</t>
-  </si>
-  <si>
-    <t>philong1410010@gmail.com</t>
-  </si>
-  <si>
-    <t>philong1410011@gmail.com</t>
-  </si>
-  <si>
     <t>Demo@124</t>
   </si>
   <si>
@@ -96,10 +73,67 @@
     <t>Demo@127</t>
   </si>
   <si>
-    <t>philong141012</t>
-  </si>
-  <si>
-    <t>philong1410012@gmail.com</t>
+    <t>philong1410013@gmail.com</t>
+  </si>
+  <si>
+    <t>Demo@128</t>
+  </si>
+  <si>
+    <t>Demo@129</t>
+  </si>
+  <si>
+    <t>Demo@130</t>
+  </si>
+  <si>
+    <t>philong1410013</t>
+  </si>
+  <si>
+    <t>Demo@131</t>
+  </si>
+  <si>
+    <t>philong141025</t>
+  </si>
+  <si>
+    <t>philong141026</t>
+  </si>
+  <si>
+    <t>philong141027</t>
+  </si>
+  <si>
+    <t>philong141028</t>
+  </si>
+  <si>
+    <t>philong141029</t>
+  </si>
+  <si>
+    <t>philong141025@gmail.com</t>
+  </si>
+  <si>
+    <t>philong141026@gmail.com</t>
+  </si>
+  <si>
+    <t>philong1410027@gmail.com</t>
+  </si>
+  <si>
+    <t>philong1410028@gmail.com</t>
+  </si>
+  <si>
+    <t>philong1410029@gmail.com</t>
+  </si>
+  <si>
+    <t>philong1410014</t>
+  </si>
+  <si>
+    <t>Demo@132</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>Trinh Tham 103</t>
+  </si>
+  <si>
+    <t>Hai Kich 103</t>
   </si>
 </sst>
 </file>
@@ -445,10 +479,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="10.21875" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" customWidth="1"/>
     <col min="4" max="4" width="26.33203125" customWidth="1"/>
@@ -482,7 +516,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
@@ -491,7 +525,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>9</v>
@@ -505,7 +539,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
         <v>7</v>
@@ -514,10 +548,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>10</v>
@@ -528,7 +562,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -537,10 +571,10 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>10</v>
@@ -551,7 +585,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
         <v>7</v>
@@ -560,10 +594,10 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>10</v>
@@ -574,7 +608,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -583,16 +617,153 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -605,9 +776,49 @@
     <hyperlink ref="D4" r:id="rId5" xr:uid="{2AFB5790-E0AD-4252-9901-B2E8CCBEDB96}"/>
     <hyperlink ref="D5" r:id="rId6" xr:uid="{D7FF85E6-8E30-4980-987F-8578F7770F43}"/>
     <hyperlink ref="E3:E6" r:id="rId7" display="Demo@123" xr:uid="{36689315-9F39-469C-B07E-C6B23AEBD54B}"/>
-    <hyperlink ref="D6" r:id="rId8" display="philong141008@gmail.com" xr:uid="{4245886C-1D95-4B35-9711-37B919C74A5B}"/>
+    <hyperlink ref="D6" r:id="rId8" xr:uid="{4245886C-1D95-4B35-9711-37B919C74A5B}"/>
+    <hyperlink ref="D7" r:id="rId9" xr:uid="{8E960DE5-6287-4915-867A-5CFE9592CC55}"/>
+    <hyperlink ref="E7:E9" r:id="rId10" display="Demo@123" xr:uid="{57B97D90-6109-4865-AB82-410D59389B38}"/>
+    <hyperlink ref="D9" r:id="rId11" xr:uid="{3B49B3EC-178F-4C4D-A1D5-7E646B3A48E7}"/>
+    <hyperlink ref="E10" r:id="rId12" display="Demo@123" xr:uid="{6B861440-800D-4EB5-B957-EEA18C05F055}"/>
+    <hyperlink ref="D11" r:id="rId13" xr:uid="{B57F3CC4-8C44-41F4-9C04-D33CFEBE72AF}"/>
+    <hyperlink ref="D12" r:id="rId14" xr:uid="{1DF60EAC-479C-4BEF-A3BB-03F78F216467}"/>
+    <hyperlink ref="E12" r:id="rId15" display="Demo@123" xr:uid="{4F78719B-828C-490F-BB4A-979E6318D4AE}"/>
+    <hyperlink ref="D13" r:id="rId16" xr:uid="{E53795D8-B14E-4084-92FD-C836BFEF0AA5}"/>
+    <hyperlink ref="E13" r:id="rId17" display="Demo@123" xr:uid="{D14E1636-2283-401F-8571-10F0E3A8CA65}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId18"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF712AEC-3E69-40E5-9E53-C946848D5F68}">
+  <dimension ref="A1:A5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>